--- a/MathAn/ell.xlsx
+++ b/MathAn/ell.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12345"/>
+    <workbookView windowWidth="28800" windowHeight="12345"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="176">
   <si>
     <t>nm</t>
   </si>
@@ -40,232 +40,229 @@
     <t>eq</t>
   </si>
   <si>
-    <t>fr</t>
+    <t>eqNum</t>
   </si>
   <si>
     <t>am</t>
   </si>
   <si>
+    <t>xc</t>
+  </si>
+  <si>
+    <t>路南区梁家屯办事处光明南路仁泰里</t>
+  </si>
+  <si>
+    <t>EOC</t>
+  </si>
+  <si>
+    <t>路南区梁家屯办事处光明南路兴泰里</t>
+  </si>
+  <si>
+    <t>路南区惠民园街道光明南路惠民园</t>
+  </si>
+  <si>
+    <t>路南区友谊里街道办事处站前路新天地美域</t>
+  </si>
+  <si>
+    <t>EOC、OLT</t>
+  </si>
+  <si>
+    <t>lb</t>
+  </si>
+  <si>
+    <t>路北区光明街道光明路凤凰世嘉</t>
+  </si>
+  <si>
     <t>ln</t>
   </si>
   <si>
+    <t>路南区万达街道文化路万达广场</t>
+  </si>
+  <si>
+    <t>路南区广场办事处学院路新华联广场</t>
+  </si>
+  <si>
+    <t>路北区大里街道大里路雅颂居</t>
+  </si>
+  <si>
+    <t>路北区翔云街道友谊路康馨雅苑</t>
+  </si>
+  <si>
+    <t>gx</t>
+  </si>
+  <si>
+    <t>路北区缸窑路办事处西窑道陶然居</t>
+  </si>
+  <si>
+    <t>路南区友谊里街道办事处光明路福乐园</t>
+  </si>
+  <si>
+    <t>CC、OLT</t>
+  </si>
+  <si>
+    <t>路北区机场路街道朝阳道裕祥园</t>
+  </si>
+  <si>
+    <t>路北区缸窑路办事处缸窑路和顺园</t>
+  </si>
+  <si>
+    <t>路北区机场路街道友谊路水电首郡</t>
+  </si>
+  <si>
+    <t>路南区金城社区燕新路金色和园</t>
+  </si>
+  <si>
+    <t>路北区机场路街道学院路荣泰尚都</t>
+  </si>
+  <si>
+    <t>路北区缸窑路办事处长宁道尚品</t>
+  </si>
+  <si>
+    <t>路南区女织寨乡吉祥路旭安园</t>
+  </si>
+  <si>
+    <t>路北区机场路街道卫国路六合轩府</t>
+  </si>
+  <si>
+    <t>高新技术开发区高新区街道办事处河茵路河茵公寓</t>
+  </si>
+  <si>
+    <t>路北区缸窑路办事处龙泽路宝龙花苑</t>
+  </si>
+  <si>
+    <t>CC</t>
+  </si>
+  <si>
+    <t>路北区兴源道办事处卫国路翔云西里龙云楼</t>
+  </si>
+  <si>
+    <t>路北区缸窑路办事处长宁道金洋御景</t>
+  </si>
+  <si>
+    <t>路北区广场办事处建设路东旭花园</t>
+  </si>
+  <si>
+    <t>路北区大里街道西山道华育3字头</t>
+  </si>
+  <si>
+    <t>路北区广场办事处北新道悦富强城</t>
+  </si>
+  <si>
+    <t>路北区高新区街道办事处建设路世纪花园</t>
+  </si>
+  <si>
+    <t>路北区机场路街道卫国路军创凯旋城</t>
+  </si>
+  <si>
+    <t>路南区广场办事处国防道国防馨苑</t>
+  </si>
+  <si>
+    <t>高新技术开发区高新区街道办事处火炬路世纪龙庭</t>
+  </si>
+  <si>
+    <t>OLT</t>
+  </si>
+  <si>
+    <t>路北区钓鱼台办事处朝阳道张各庄楼</t>
+  </si>
+  <si>
+    <t>路北区大里街道学院路天一广场</t>
+  </si>
+  <si>
+    <t>路北区大里街道学院路中环广场</t>
+  </si>
+  <si>
+    <t>高新技术开发区高新区街道办事处建设路世纪瑞庭</t>
+  </si>
+  <si>
+    <t>路北区钓鱼台办事处裕华道凤祥园</t>
+  </si>
+  <si>
+    <t>路南区果园乡站前路瑞安园</t>
+  </si>
+  <si>
+    <t>路南区友谊里街道办事处光明路时代花园</t>
+  </si>
+  <si>
+    <t>路北区光明街道光明路石油家园</t>
+  </si>
+  <si>
+    <t>路北区东新村街道城山路公园艺景</t>
+  </si>
+  <si>
+    <t>cj</t>
+  </si>
+  <si>
+    <t>路北区韩城镇西欢坨</t>
+  </si>
+  <si>
+    <t>路北区河北路办事处河北路和泓阳光北岸</t>
+  </si>
+  <si>
+    <t>路北区河北路办事处河北路河北一号</t>
+  </si>
+  <si>
+    <t>路北区乔屯街道文化路凤凰楼(开滦)</t>
+  </si>
+  <si>
+    <t>路南区稻地镇刘唐保</t>
+  </si>
+  <si>
+    <t>路南区文北街道新华道水岸东方</t>
+  </si>
+  <si>
     <t>路北区大里街道卫国路凤城国贸</t>
   </si>
   <si>
-    <t>CC</t>
-  </si>
-  <si>
-    <t>电表</t>
-  </si>
-  <si>
-    <t>xc</t>
-  </si>
-  <si>
-    <t>路北区大里街道西山道华育3字头</t>
-  </si>
-  <si>
-    <t>路北区大里街道学院路天一广场</t>
-  </si>
-  <si>
-    <t>路北区大里街道学院路中环广场</t>
-  </si>
-  <si>
-    <t>gx</t>
-  </si>
-  <si>
-    <t>路北区缸窑路办事处龙泽路宝龙花苑</t>
-  </si>
-  <si>
-    <t>lb</t>
-  </si>
-  <si>
-    <t>路北区高新区街道办事处建设路世纪花园</t>
-  </si>
-  <si>
-    <t>路北区机场路街道卫国路军创凯旋城</t>
+    <t>高新技术开发区高新区街道办事处龙富南道恒大学庭一期</t>
+  </si>
+  <si>
+    <t>路北区大里街道学院路军安里建科楼</t>
+  </si>
+  <si>
+    <t>路北区光明街道光明路繁荣花园</t>
+  </si>
+  <si>
+    <t>路北区广场办事处北新道富强楼</t>
+  </si>
+  <si>
+    <t>路北区果园乡刘火新庄</t>
+  </si>
+  <si>
+    <t>路北区机场路街道朝阳道机北楼(供电)</t>
+  </si>
+  <si>
+    <t>路北区机场路街道长宁道祥和里</t>
+  </si>
+  <si>
+    <t>路北区乔屯街道龙泽南路凤东楼</t>
+  </si>
+  <si>
+    <t>路北区乔屯街道文化路文化楼</t>
+  </si>
+  <si>
+    <t>路北区乔屯街道文化路西北新楼</t>
+  </si>
+  <si>
+    <t>路南区马家屯街道南新道渔人码头二期</t>
+  </si>
+  <si>
+    <t>路南区女织寨乡复兴路女织寨乡侯边庄</t>
   </si>
   <si>
     <t>路北区龙东街道办事处龙泽路龙悦新居</t>
   </si>
   <si>
-    <t>路南区女织寨乡吉祥路旭安园</t>
-  </si>
-  <si>
-    <t>CC、OLT</t>
-  </si>
-  <si>
-    <t>路北区缸窑路办事处缸窑路和顺园</t>
-  </si>
-  <si>
     <t>路北区光明街道友谊路德源里</t>
   </si>
   <si>
     <t>路北区光明街道友谊路德源里增楼</t>
   </si>
   <si>
-    <t>路北区广场办事处北新道悦富强城</t>
-  </si>
-  <si>
-    <t>路南区友谊里街道办事处光明路福乐园</t>
-  </si>
-  <si>
-    <t>高新技术开发区高新区街道办事处河茵路河茵公寓</t>
-  </si>
-  <si>
-    <t>EOC</t>
-  </si>
-  <si>
-    <t>路北区大里街道大里路雅颂居</t>
-  </si>
-  <si>
-    <t>路北区缸窑路办事处长宁道金洋御景</t>
-  </si>
-  <si>
-    <t>路北区光明街道光明路凤凰世嘉</t>
-  </si>
-  <si>
-    <t>路北区广场办事处建设路东旭花园</t>
-  </si>
-  <si>
-    <t>路北区机场路街道朝阳道裕祥园</t>
-  </si>
-  <si>
-    <t>路北区机场路街道卫国路六合轩府</t>
-  </si>
-  <si>
-    <t>路北区机场路街道学院路荣泰尚都</t>
-  </si>
-  <si>
-    <t>路北区机场路街道友谊路水电首郡</t>
-  </si>
-  <si>
-    <t>路北区翔云街道友谊路康馨雅苑</t>
-  </si>
-  <si>
-    <t>路北区兴源道办事处卫国路翔云西里龙云楼</t>
-  </si>
-  <si>
-    <t>路南区广场办事处国防道国防馨苑</t>
-  </si>
-  <si>
-    <t>路南区广场办事处学院路新华联广场</t>
-  </si>
-  <si>
-    <t>路南区惠民园街道光明南路惠民园</t>
-  </si>
-  <si>
-    <t>路南区金城社区燕新路金色和园</t>
-  </si>
-  <si>
-    <t>路南区梁家屯办事处光明南路仁泰里</t>
-  </si>
-  <si>
-    <t>路南区梁家屯办事处光明南路兴泰里</t>
-  </si>
-  <si>
-    <t>路南区万达街道文化路万达广场</t>
-  </si>
-  <si>
-    <t>路北区缸窑路办事处西窑道陶然居</t>
-  </si>
-  <si>
-    <t>EOC、OLT</t>
-  </si>
-  <si>
-    <t>路北区缸窑路办事处长宁道尚品</t>
-  </si>
-  <si>
-    <t>路北区光明街道光明路石油家园</t>
-  </si>
-  <si>
-    <t>路南区友谊里街道办事处站前路新天地美域</t>
-  </si>
-  <si>
     <t>路北区钓鱼台办事处朝阳道裕华嘉苑(供电)</t>
   </si>
   <si>
     <t>路南区马家屯街道复兴路荷花盛世</t>
-  </si>
-  <si>
-    <t>高新技术开发区高新区街道办事处龙富南道恒大学庭一期</t>
-  </si>
-  <si>
-    <t>OLT</t>
-  </si>
-  <si>
-    <t>路北区大里街道学院路军安里建科楼</t>
-  </si>
-  <si>
-    <t>路北区光明街道光明路繁荣花园</t>
-  </si>
-  <si>
-    <t>路北区广场办事处北新道富强楼</t>
-  </si>
-  <si>
-    <t>cj</t>
-  </si>
-  <si>
-    <t>路北区果园乡刘火新庄</t>
-  </si>
-  <si>
-    <t>路北区机场路街道朝阳道机北楼(供电)</t>
-  </si>
-  <si>
-    <t>路北区机场路街道长宁道祥和里</t>
-  </si>
-  <si>
-    <t>路北区乔屯街道龙泽南路凤东楼</t>
-  </si>
-  <si>
-    <t>路北区乔屯街道文化路文化楼</t>
-  </si>
-  <si>
-    <t>路北区乔屯街道文化路西北新楼</t>
-  </si>
-  <si>
-    <t>路南区马家屯街道南新道渔人码头二期</t>
-  </si>
-  <si>
-    <t>路南区女织寨乡复兴路女织寨乡侯边庄</t>
-  </si>
-  <si>
-    <t>路北区东新村街道城山路公园艺景</t>
-  </si>
-  <si>
-    <t>路北区韩城镇西欢坨</t>
-  </si>
-  <si>
-    <t>路北区河北路办事处河北路和泓阳光北岸</t>
-  </si>
-  <si>
-    <t>路北区河北路办事处河北路河北一号</t>
-  </si>
-  <si>
-    <t>路北区乔屯街道文化路凤凰楼(开滦)</t>
-  </si>
-  <si>
-    <t>路南区稻地镇刘唐保</t>
-  </si>
-  <si>
-    <t>路南区文北街道新华道水岸东方</t>
-  </si>
-  <si>
-    <t>高新技术开发区高新区街道办事处建设路世纪瑞庭</t>
-  </si>
-  <si>
-    <t>路北区钓鱼台办事处裕华道凤祥园</t>
-  </si>
-  <si>
-    <t>路南区果园乡站前路瑞安园</t>
-  </si>
-  <si>
-    <t>路南区友谊里街道办事处光明路时代花园</t>
-  </si>
-  <si>
-    <t>高新技术开发区高新区街道办事处火炬路世纪龙庭</t>
-  </si>
-  <si>
-    <t>路北区钓鱼台办事处朝阳道张各庄楼</t>
   </si>
   <si>
     <t>高新技术开发区高新区街道办事处火炬路凤城阳光</t>
@@ -557,7 +554,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -568,13 +565,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1042,46 +1032,49 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1093,97 +1086,94 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1549,7 +1539,7 @@
     <col min="5" max="5" width="3.625" customWidth="1"/>
     <col min="6" max="7" width="4.75" customWidth="1"/>
     <col min="8" max="8" width="9.25" customWidth="1"/>
-    <col min="9" max="9" width="5.125" customWidth="1"/>
+    <col min="9" max="9" width="7" customWidth="1"/>
     <col min="10" max="10" width="9.375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1593,16 +1583,16 @@
         <v>11</v>
       </c>
       <c r="C2" s="2">
-        <v>77</v>
+        <v>1549</v>
       </c>
       <c r="D2" s="2">
-        <v>10</v>
+        <v>718</v>
       </c>
       <c r="E2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -1610,31 +1600,32 @@
       <c r="H2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>13</v>
+      <c r="I2" s="2">
+        <f>SUM(E2:G2)+1</f>
+        <v>292</v>
       </c>
       <c r="J2" s="2">
-        <v>5500</v>
+        <v>22298.76</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C3" s="2">
-        <v>166</v>
+        <v>1117</v>
       </c>
       <c r="D3" s="2">
-        <v>67</v>
+        <v>667</v>
       </c>
       <c r="E3" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -1642,11 +1633,12 @@
       <c r="H3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>13</v>
+      <c r="I3" s="2">
+        <f>SUM(E3:G3)+1</f>
+        <v>207</v>
       </c>
       <c r="J3" s="2">
-        <v>960</v>
+        <v>33020</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1654,19 +1646,19 @@
         <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C4" s="2">
-        <v>5</v>
+        <v>2018</v>
       </c>
       <c r="D4" s="2">
-        <v>3</v>
+        <v>615</v>
       </c>
       <c r="E4" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -1674,11 +1666,12 @@
       <c r="H4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>13</v>
+      <c r="I4" s="2">
+        <f>SUM(E4:G4)+1</f>
+        <v>181</v>
       </c>
       <c r="J4" s="2">
-        <v>2600</v>
+        <v>34675</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1686,51 +1679,52 @@
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C5" s="2">
-        <v>18</v>
+        <v>816</v>
       </c>
       <c r="D5" s="2">
-        <v>9</v>
+        <v>505</v>
       </c>
       <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>117</v>
+      </c>
+      <c r="G5" s="2">
         <v>3</v>
       </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="I5" s="2">
+        <f>SUM(E5:G5)+1</f>
+        <v>121</v>
       </c>
       <c r="J5" s="2">
-        <v>2612</v>
+        <v>14089</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="C6" s="2">
-        <v>31</v>
+        <v>597</v>
       </c>
       <c r="D6" s="2">
-        <v>26</v>
+        <v>213</v>
       </c>
       <c r="E6" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
@@ -1738,31 +1732,32 @@
       <c r="H6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>13</v>
+      <c r="I6" s="2">
+        <f>SUM(E6:G6)+1</f>
+        <v>86</v>
       </c>
       <c r="J6" s="2">
-        <v>10635</v>
+        <v>32392</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="C7" s="2">
-        <v>155</v>
+        <v>699</v>
       </c>
       <c r="D7" s="2">
-        <v>26</v>
+        <v>188</v>
       </c>
       <c r="E7" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
@@ -1770,31 +1765,32 @@
       <c r="H7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>13</v>
+      <c r="I7" s="2">
+        <f>SUM(E7:G7)+1</f>
+        <v>70</v>
       </c>
       <c r="J7" s="2">
-        <v>6574</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" s="2">
-        <v>28</v>
+        <v>347</v>
       </c>
       <c r="D8" s="2">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="E8" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
@@ -1802,31 +1798,32 @@
       <c r="H8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>13</v>
+      <c r="I8" s="2">
+        <f>SUM(E8:G8)+1</f>
+        <v>42</v>
       </c>
       <c r="J8" s="2">
-        <v>3000</v>
+        <v>14729</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="2">
-        <v>67</v>
+        <v>852</v>
       </c>
       <c r="D9" s="2">
-        <v>2</v>
+        <v>231</v>
       </c>
       <c r="E9" s="2">
         <v>0</v>
       </c>
       <c r="F9" s="2">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
@@ -1834,156 +1831,161 @@
       <c r="H9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>13</v>
+      <c r="I9" s="2">
+        <f>SUM(E9:G9)+1</f>
+        <v>40</v>
       </c>
       <c r="J9" s="2">
-        <v>945.96</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2">
-        <v>432</v>
+        <v>188</v>
       </c>
       <c r="D10" s="2">
-        <v>322</v>
+        <v>31</v>
       </c>
       <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
+        <v>36</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2">
-        <v>3</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>13</v>
+      <c r="I10" s="2">
+        <f>SUM(E10:G10)+1</f>
+        <v>37</v>
       </c>
       <c r="J10" s="2">
-        <v>12036</v>
+        <v>4544</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" s="2">
-        <v>457</v>
+        <v>365</v>
       </c>
       <c r="D11" s="2">
-        <v>302</v>
+        <v>81</v>
       </c>
       <c r="E11" s="2">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="I11" s="2">
+        <f>SUM(E11:G11)+1</f>
+        <v>32</v>
       </c>
       <c r="J11" s="2">
-        <v>16779.6</v>
+        <v>6221</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="2">
+        <v>511</v>
+      </c>
+      <c r="D12" s="2">
+        <v>283</v>
+      </c>
+      <c r="E12" s="2">
+        <v>30</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="2">
-        <v>492</v>
-      </c>
-      <c r="D12" s="2">
-        <v>245</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
-      <c r="G12" s="2">
-        <v>0</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>13</v>
+      <c r="I12" s="2">
+        <f>SUM(E12:G12)+1</f>
+        <v>31</v>
       </c>
       <c r="J12" s="2">
-        <v>7420</v>
+        <v>38400</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C13" s="2">
+        <v>150</v>
+      </c>
+      <c r="D13" s="2">
+        <v>38</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>30</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="2">
-        <v>4</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
-      <c r="G13" s="2">
-        <v>0</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>13</v>
+      <c r="I13" s="2">
+        <f>SUM(E13:G13)+1</f>
+        <v>31</v>
       </c>
       <c r="J13" s="2">
-        <v>71.18</v>
+        <v>7631</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C14" s="2">
-        <v>135</v>
+        <v>457</v>
       </c>
       <c r="D14" s="2">
-        <v>161</v>
+        <v>302</v>
       </c>
       <c r="E14" s="2">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -1992,365 +1994,377 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="I14" s="2">
+        <f>SUM(E14:G14)+1</f>
+        <v>29</v>
       </c>
       <c r="J14" s="2">
-        <v>20000</v>
+        <v>16779.6</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="2">
-        <v>511</v>
+        <v>115</v>
       </c>
       <c r="D15" s="2">
-        <v>283</v>
+        <v>45</v>
       </c>
       <c r="E15" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="I15" s="2">
+        <f>SUM(E15:G15)+1</f>
+        <v>29</v>
       </c>
       <c r="J15" s="2">
-        <v>38400</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C16" s="2">
-        <v>67</v>
+        <v>133</v>
       </c>
       <c r="D16" s="2">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="E16" s="2">
         <v>0</v>
       </c>
       <c r="F16" s="2">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G16" s="2">
         <v>0</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="I16" s="2">
+        <f>SUM(E16:G16)+1</f>
+        <v>29</v>
       </c>
       <c r="J16" s="2">
-        <v>2800</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17" s="2">
-        <v>852</v>
+        <v>101</v>
       </c>
       <c r="D17" s="2">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="E17" s="2">
         <v>0</v>
       </c>
       <c r="F17" s="2">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="G17" s="2">
         <v>0</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="I17" s="2">
+        <f>SUM(E17:G17)+1</f>
+        <v>24</v>
       </c>
       <c r="J17" s="2">
-        <v>8500</v>
+        <v>8865</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18" s="2">
-        <v>40</v>
+        <v>180</v>
       </c>
       <c r="D18" s="2">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="E18" s="2">
         <v>0</v>
       </c>
       <c r="F18" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="I18" s="2">
+        <f>SUM(E18:G18)+1</f>
+        <v>19</v>
       </c>
       <c r="J18" s="2">
-        <v>3600</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C19" s="2">
-        <v>597</v>
+        <v>432</v>
       </c>
       <c r="D19" s="2">
-        <v>213</v>
+        <v>322</v>
       </c>
       <c r="E19" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F19" s="2">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="I19" s="2">
+        <f>SUM(E19:G19)+1</f>
+        <v>16</v>
       </c>
       <c r="J19" s="2">
-        <v>32392</v>
+        <v>12036</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20" s="2">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="D20" s="2">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E20" s="2">
         <v>0</v>
       </c>
       <c r="F20" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G20" s="2">
         <v>0</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="I20" s="2">
+        <f>SUM(E20:G20)+1</f>
+        <v>15</v>
       </c>
       <c r="J20" s="2">
-        <v>1980</v>
+        <v>3552</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C21" s="2">
-        <v>150</v>
+        <v>67</v>
       </c>
       <c r="D21" s="2">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E21" s="2">
         <v>0</v>
       </c>
       <c r="F21" s="2">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="G21" s="2">
         <v>0</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="I21" s="2">
+        <f>SUM(E21:G21)+1</f>
+        <v>12</v>
       </c>
       <c r="J21" s="2">
-        <v>7631</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="2">
+        <v>31</v>
+      </c>
+      <c r="D22" s="2">
+        <v>26</v>
+      </c>
+      <c r="E22" s="2">
+        <v>10</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="2">
-        <v>106</v>
-      </c>
-      <c r="D22" s="2">
-        <v>31</v>
-      </c>
-      <c r="E22" s="2">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2">
-        <v>14</v>
-      </c>
-      <c r="G22" s="2">
-        <v>0</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>13</v>
+      <c r="I22" s="2">
+        <f>SUM(E22:G22)+1</f>
+        <v>11</v>
       </c>
       <c r="J22" s="2">
-        <v>3552</v>
+        <v>10635</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C23" s="2">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="D23" s="2">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E23" s="2">
         <v>0</v>
       </c>
       <c r="F23" s="2">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G23" s="2">
         <v>0</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="I23" s="2">
+        <f>SUM(E23:G23)+1</f>
+        <v>11</v>
       </c>
       <c r="J23" s="2">
-        <v>8865</v>
+        <v>600</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C24" s="2">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="D24" s="2">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="E24" s="2">
         <v>0</v>
       </c>
       <c r="F24" s="2">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G24" s="2">
         <v>0</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="I24" s="2">
+        <f>SUM(E24:G24)+1</f>
+        <v>10</v>
       </c>
       <c r="J24" s="2">
-        <v>11000</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C25" s="2">
-        <v>188</v>
+        <v>58</v>
       </c>
       <c r="D25" s="2">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E25" s="2">
         <v>0</v>
       </c>
       <c r="F25" s="2">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="G25" s="2">
         <v>0</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="I25" s="2">
+        <f>SUM(E25:G25)+1</f>
+        <v>9</v>
       </c>
       <c r="J25" s="2">
-        <v>4544</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -2361,394 +2375,406 @@
         <v>42</v>
       </c>
       <c r="C26" s="2">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="D26" s="2">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="E26" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F26" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2">
         <v>0</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>13</v>
+        <v>38</v>
+      </c>
+      <c r="I26" s="2">
+        <f>SUM(E26:G26)+1</f>
+        <v>7</v>
       </c>
       <c r="J26" s="2">
-        <v>600</v>
+        <v>960</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C27" s="2">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="D27" s="2">
-        <v>35</v>
+        <v>161</v>
       </c>
       <c r="E27" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F27" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G27" s="2">
         <v>0</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="I27" s="2">
+        <f>SUM(E27:G27)+1</f>
+        <v>7</v>
       </c>
       <c r="J27" s="2">
-        <v>1920</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C28" s="2">
-        <v>347</v>
+        <v>155</v>
       </c>
       <c r="D28" s="2">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="E28" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F28" s="2">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G28" s="2">
         <v>0</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>13</v>
+        <v>38</v>
+      </c>
+      <c r="I28" s="2">
+        <f>SUM(E28:G28)+1</f>
+        <v>6</v>
       </c>
       <c r="J28" s="2">
-        <v>14729</v>
+        <v>6574</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C29" s="2">
-        <v>2018</v>
+        <v>28</v>
       </c>
       <c r="D29" s="2">
-        <v>615</v>
+        <v>7</v>
       </c>
       <c r="E29" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F29" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G29" s="2">
         <v>0</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>13</v>
+        <v>38</v>
+      </c>
+      <c r="I29" s="2">
+        <f>SUM(E29:G29)+1</f>
+        <v>6</v>
       </c>
       <c r="J29" s="2">
-        <v>34675</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C30" s="2">
-        <v>133</v>
+        <v>53</v>
       </c>
       <c r="D30" s="2">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="E30" s="2">
         <v>0</v>
       </c>
       <c r="F30" s="2">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="G30" s="2">
         <v>0</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="I30" s="2">
+        <f>SUM(E30:G30)+1</f>
+        <v>5</v>
       </c>
       <c r="J30" s="2">
-        <v>7200</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C31" s="2">
-        <v>1549</v>
+        <v>276</v>
       </c>
       <c r="D31" s="2">
-        <v>718</v>
+        <v>95</v>
       </c>
       <c r="E31" s="2">
         <v>0</v>
       </c>
       <c r="F31" s="2">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="G31" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I31" s="2">
+        <f>SUM(E31:G31)+1</f>
+        <v>5</v>
       </c>
       <c r="J31" s="2">
-        <v>22298.76</v>
+        <v>10800</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C32" s="2">
-        <v>1117</v>
+        <v>237</v>
       </c>
       <c r="D32" s="2">
-        <v>667</v>
+        <v>64</v>
       </c>
       <c r="E32" s="2">
         <v>0</v>
       </c>
       <c r="F32" s="2">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="G32" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I32" s="2">
+        <f>SUM(E32:G32)+1</f>
+        <v>5</v>
       </c>
       <c r="J32" s="2">
-        <v>33020</v>
+        <v>3159.68</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C33" s="2">
-        <v>699</v>
+        <v>5</v>
       </c>
       <c r="D33" s="2">
-        <v>188</v>
+        <v>3</v>
       </c>
       <c r="E33" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F33" s="2">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="G33" s="2">
         <v>0</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>13</v>
+        <v>38</v>
+      </c>
+      <c r="I33" s="2">
+        <f>SUM(E33:G33)+1</f>
+        <v>4</v>
       </c>
       <c r="J33" s="2">
-        <v>16000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" s="2">
         <v>18</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C34" s="2">
-        <v>365</v>
-      </c>
       <c r="D34" s="2">
-        <v>81</v>
+        <v>9</v>
       </c>
       <c r="E34" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F34" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>13</v>
+        <v>38</v>
+      </c>
+      <c r="I34" s="2">
+        <f>SUM(E34:G34)+1</f>
+        <v>4</v>
       </c>
       <c r="J34" s="2">
-        <v>6221</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C35" s="2">
-        <v>180</v>
+        <v>76</v>
       </c>
       <c r="D35" s="2">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="E35" s="2">
         <v>0</v>
       </c>
       <c r="F35" s="2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G35" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I35" s="2">
+        <f>SUM(E35:G35)+1</f>
+        <v>4</v>
       </c>
       <c r="J35" s="2">
-        <v>10000</v>
+        <v>2751.6</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C36" s="2">
-        <v>334</v>
+        <v>255</v>
       </c>
       <c r="D36" s="2">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="E36" s="2">
         <v>0</v>
       </c>
       <c r="F36" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I36" s="2">
+        <f>SUM(E36:G36)+1</f>
+        <v>4</v>
       </c>
       <c r="J36" s="2">
-        <v>2930</v>
+        <v>196.88</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C37" s="2">
-        <v>816</v>
+        <v>297</v>
       </c>
       <c r="D37" s="2">
-        <v>505</v>
+        <v>300</v>
       </c>
       <c r="E37" s="2">
         <v>0</v>
       </c>
       <c r="F37" s="2">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="G37" s="2">
         <v>3</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I37" s="2">
+        <f>SUM(E37:G37)+1</f>
+        <v>4</v>
       </c>
       <c r="J37" s="2">
-        <v>14089</v>
+        <v>4142</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="2" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C38" s="2">
-        <v>109</v>
+        <v>163</v>
       </c>
       <c r="D38" s="2">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="E38" s="2">
         <v>0</v>
@@ -2757,62 +2783,64 @@
         <v>0</v>
       </c>
       <c r="G38" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I38" s="2">
+        <f>SUM(E38:G38)+1</f>
+        <v>4</v>
       </c>
       <c r="J38" s="2">
-        <v>163.03</v>
+        <v>11472</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C39" s="2">
-        <v>51</v>
+        <v>334</v>
       </c>
       <c r="D39" s="2">
-        <v>39</v>
+        <v>115</v>
       </c>
       <c r="E39" s="2">
         <v>0</v>
       </c>
       <c r="F39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="I39" s="2">
+        <f>SUM(E39:G39)+1</f>
+        <v>3</v>
       </c>
       <c r="J39" s="2">
-        <v>1850</v>
+        <v>2930</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C40" s="2">
-        <v>55</v>
+        <v>136</v>
       </c>
       <c r="D40" s="2">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E40" s="2">
         <v>0</v>
@@ -2821,30 +2849,31 @@
         <v>0</v>
       </c>
       <c r="G40" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I40" s="2">
+        <f>SUM(E40:G40)+1</f>
+        <v>3</v>
       </c>
       <c r="J40" s="2">
-        <v>6000</v>
+        <v>7012</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="2" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C41" s="2">
-        <v>200</v>
+        <v>43</v>
       </c>
       <c r="D41" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E41" s="2">
         <v>0</v>
@@ -2853,30 +2882,31 @@
         <v>0</v>
       </c>
       <c r="G41" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I41" s="2">
+        <f>SUM(E41:G41)+1</f>
+        <v>3</v>
       </c>
       <c r="J41" s="2">
-        <v>3024</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C42" s="2">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="D42" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E42" s="2">
         <v>0</v>
@@ -2885,30 +2915,31 @@
         <v>0</v>
       </c>
       <c r="G42" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I42" s="2">
+        <f>SUM(E42:G42)+1</f>
+        <v>3</v>
       </c>
       <c r="J42" s="2">
-        <v>2200</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="2" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C43" s="2">
-        <v>141</v>
+        <v>687</v>
       </c>
       <c r="D43" s="2">
-        <v>65</v>
+        <v>295</v>
       </c>
       <c r="E43" s="2">
         <v>0</v>
@@ -2917,30 +2948,31 @@
         <v>0</v>
       </c>
       <c r="G43" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I43" s="2">
+        <f>SUM(E43:G43)+1</f>
+        <v>3</v>
       </c>
       <c r="J43" s="2">
-        <v>6000</v>
+        <v>10026</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="C44" s="2">
-        <v>345</v>
+        <v>56</v>
       </c>
       <c r="D44" s="2">
-        <v>291</v>
+        <v>27</v>
       </c>
       <c r="E44" s="2">
         <v>0</v>
@@ -2949,30 +2981,31 @@
         <v>0</v>
       </c>
       <c r="G44" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I44" s="2">
+        <f>SUM(E44:G44)+1</f>
+        <v>3</v>
       </c>
       <c r="J44" s="2">
-        <v>1304</v>
+        <v>780</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="2" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C45" s="2">
-        <v>246</v>
+        <v>279</v>
       </c>
       <c r="D45" s="2">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="E45" s="2">
         <v>0</v>
@@ -2981,30 +3014,31 @@
         <v>0</v>
       </c>
       <c r="G45" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I45" s="2">
+        <f>SUM(E45:G45)+1</f>
+        <v>3</v>
       </c>
       <c r="J45" s="2">
-        <v>2067.73</v>
+        <v>5580</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C46" s="2">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="D46" s="2">
-        <v>274</v>
+        <v>113</v>
       </c>
       <c r="E46" s="2">
         <v>0</v>
@@ -3013,62 +3047,64 @@
         <v>0</v>
       </c>
       <c r="G46" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I46" s="2">
+        <f>SUM(E46:G46)+1</f>
+        <v>3</v>
       </c>
       <c r="J46" s="2">
-        <v>1042.68</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C47" s="2">
+        <v>77</v>
+      </c>
+      <c r="D47" s="2">
         <v>10</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C47" s="2">
-        <v>117</v>
-      </c>
-      <c r="D47" s="2">
-        <v>82</v>
-      </c>
       <c r="E47" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="2">
         <v>0</v>
       </c>
       <c r="G47" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>13</v>
+        <v>38</v>
+      </c>
+      <c r="I47" s="2">
+        <f>SUM(E47:G47)+1</f>
+        <v>2</v>
       </c>
       <c r="J47" s="2">
-        <v>1920</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C48" s="2">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="D48" s="2">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="E48" s="2">
         <v>0</v>
@@ -3080,27 +3116,28 @@
         <v>1</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I48" s="2">
+        <f>SUM(E48:G48)+1</f>
+        <v>2</v>
       </c>
       <c r="J48" s="2">
-        <v>1920</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C49" s="2">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="D49" s="2">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="E49" s="2">
         <v>0</v>
@@ -3112,13 +3149,14 @@
         <v>1</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I49" s="2">
+        <f>SUM(E49:G49)+1</f>
+        <v>2</v>
       </c>
       <c r="J49" s="2">
-        <v>840</v>
+        <v>3024</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -3126,13 +3164,13 @@
         <v>10</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C50" s="2">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D50" s="2">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="E50" s="2">
         <v>0</v>
@@ -3144,27 +3182,28 @@
         <v>1</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I50" s="2">
+        <f>SUM(E50:G50)+1</f>
+        <v>2</v>
       </c>
       <c r="J50" s="2">
-        <v>1000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="2" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C51" s="2">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="D51" s="2">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E51" s="2">
         <v>0</v>
@@ -3176,27 +3215,28 @@
         <v>1</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I51" s="2">
+        <f>SUM(E51:G51)+1</f>
+        <v>2</v>
       </c>
       <c r="J51" s="2">
-        <v>700</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="2" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C52" s="2">
-        <v>136</v>
+        <v>345</v>
       </c>
       <c r="D52" s="2">
-        <v>65</v>
+        <v>291</v>
       </c>
       <c r="E52" s="2">
         <v>0</v>
@@ -3205,30 +3245,31 @@
         <v>0</v>
       </c>
       <c r="G52" s="2">
+        <v>1</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I52" s="2">
+        <f>SUM(E52:G52)+1</f>
         <v>2</v>
       </c>
-      <c r="H52" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="J52" s="2">
-        <v>7012</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="2" t="s">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C53" s="2">
-        <v>43</v>
+        <v>246</v>
       </c>
       <c r="D53" s="2">
-        <v>9</v>
+        <v>145</v>
       </c>
       <c r="E53" s="2">
         <v>0</v>
@@ -3237,30 +3278,31 @@
         <v>0</v>
       </c>
       <c r="G53" s="2">
+        <v>1</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I53" s="2">
+        <f>SUM(E53:G53)+1</f>
         <v>2</v>
       </c>
-      <c r="H53" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="J53" s="2">
-        <v>2600</v>
+        <v>2067.73</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C54" s="2">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="D54" s="2">
-        <v>34</v>
+        <v>274</v>
       </c>
       <c r="E54" s="2">
         <v>0</v>
@@ -3269,30 +3311,31 @@
         <v>0</v>
       </c>
       <c r="G54" s="2">
+        <v>1</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I54" s="2">
+        <f>SUM(E54:G54)+1</f>
         <v>2</v>
       </c>
-      <c r="H54" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="J54" s="2">
-        <v>1800</v>
+        <v>1042.68</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C55" s="2">
-        <v>687</v>
+        <v>117</v>
       </c>
       <c r="D55" s="2">
-        <v>295</v>
+        <v>82</v>
       </c>
       <c r="E55" s="2">
         <v>0</v>
@@ -3301,30 +3344,31 @@
         <v>0</v>
       </c>
       <c r="G55" s="2">
+        <v>1</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I55" s="2">
+        <f>SUM(E55:G55)+1</f>
         <v>2</v>
       </c>
-      <c r="H55" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="J55" s="2">
-        <v>10026</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C56" s="2">
-        <v>56</v>
+        <v>150</v>
       </c>
       <c r="D56" s="2">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="E56" s="2">
         <v>0</v>
@@ -3333,30 +3377,31 @@
         <v>0</v>
       </c>
       <c r="G56" s="2">
+        <v>1</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I56" s="2">
+        <f>SUM(E56:G56)+1</f>
         <v>2</v>
       </c>
-      <c r="H56" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="J56" s="2">
-        <v>780</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="2" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C57" s="2">
-        <v>279</v>
+        <v>160</v>
       </c>
       <c r="D57" s="2">
-        <v>175</v>
+        <v>60</v>
       </c>
       <c r="E57" s="2">
         <v>0</v>
@@ -3365,30 +3410,31 @@
         <v>0</v>
       </c>
       <c r="G57" s="2">
+        <v>1</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I57" s="2">
+        <f>SUM(E57:G57)+1</f>
         <v>2</v>
       </c>
-      <c r="H57" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="J57" s="2">
-        <v>5580</v>
+        <v>840</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C58" s="2">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="D58" s="2">
-        <v>113</v>
+        <v>61</v>
       </c>
       <c r="E58" s="2">
         <v>0</v>
@@ -3397,30 +3443,31 @@
         <v>0</v>
       </c>
       <c r="G58" s="2">
+        <v>1</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I58" s="2">
+        <f>SUM(E58:G58)+1</f>
         <v>2</v>
       </c>
-      <c r="H58" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="J58" s="2">
-        <v>2586</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="2" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C59" s="2">
-        <v>76</v>
+        <v>153</v>
       </c>
       <c r="D59" s="2">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E59" s="2">
         <v>0</v>
@@ -3429,30 +3476,31 @@
         <v>0</v>
       </c>
       <c r="G59" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I59" s="2">
+        <f>SUM(E59:G59)+1</f>
+        <v>2</v>
       </c>
       <c r="J59" s="2">
-        <v>2751.6</v>
+        <v>700</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C60" s="2">
-        <v>255</v>
+        <v>67</v>
       </c>
       <c r="D60" s="2">
-        <v>121</v>
+        <v>2</v>
       </c>
       <c r="E60" s="2">
         <v>0</v>
@@ -3461,30 +3509,31 @@
         <v>0</v>
       </c>
       <c r="G60" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>13</v>
+        <v>38</v>
+      </c>
+      <c r="I60" s="2">
+        <f>SUM(E60:G60)+1</f>
+        <v>1</v>
       </c>
       <c r="J60" s="2">
-        <v>196.88</v>
+        <v>945.96</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C61" s="2">
-        <v>297</v>
+        <v>492</v>
       </c>
       <c r="D61" s="2">
-        <v>300</v>
+        <v>245</v>
       </c>
       <c r="E61" s="2">
         <v>0</v>
@@ -3493,30 +3542,31 @@
         <v>0</v>
       </c>
       <c r="G61" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="I61" s="2">
+        <f>SUM(E61:G61)+1</f>
+        <v>1</v>
       </c>
       <c r="J61" s="2">
-        <v>4142</v>
+        <v>7420</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C62" s="2">
-        <v>163</v>
+        <v>12</v>
       </c>
       <c r="D62" s="2">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="E62" s="2">
         <v>0</v>
@@ -3525,30 +3575,31 @@
         <v>0</v>
       </c>
       <c r="G62" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I62" s="2" t="s">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="I62" s="2">
+        <f>SUM(E62:G62)+1</f>
+        <v>1</v>
       </c>
       <c r="J62" s="2">
-        <v>11472</v>
+        <v>71.18</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C63" s="2">
-        <v>276</v>
+        <v>109</v>
       </c>
       <c r="D63" s="2">
-        <v>95</v>
+        <v>15</v>
       </c>
       <c r="E63" s="2">
         <v>0</v>
@@ -3557,30 +3608,31 @@
         <v>0</v>
       </c>
       <c r="G63" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I63" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="I63" s="2">
+        <f>SUM(E63:G63)+1</f>
+        <v>1</v>
       </c>
       <c r="J63" s="2">
-        <v>10800</v>
+        <v>163.03</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C64" s="2">
-        <v>237</v>
+        <v>51</v>
       </c>
       <c r="D64" s="2">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="E64" s="2">
         <v>0</v>
@@ -3589,24 +3641,25 @@
         <v>0</v>
       </c>
       <c r="G64" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I64" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="I64" s="2">
+        <f>SUM(E64:G64)+1</f>
+        <v>1</v>
       </c>
       <c r="J64" s="2">
-        <v>3159.68</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C65" s="2">
         <v>12</v>
@@ -3624,10 +3677,11 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I65" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I65" s="2">
+        <f>SUM(E65:G65)+1</f>
+        <v>1</v>
       </c>
       <c r="J65" s="2">
         <v>600</v>
@@ -3635,10 +3689,10 @@
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C66" s="2">
         <v>164</v>
@@ -3656,10 +3710,11 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I66" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I66" s="2">
+        <f>SUM(E66:G66)+1</f>
+        <v>1</v>
       </c>
       <c r="J66" s="2">
         <v>10800</v>
@@ -3667,10 +3722,10 @@
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C67" s="2">
         <v>56</v>
@@ -3688,10 +3743,11 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I67" s="2">
+        <f t="shared" ref="I67:I98" si="0">SUM(E67:G67)+1</f>
+        <v>1</v>
       </c>
       <c r="J67" s="2">
         <v>2875</v>
@@ -3699,10 +3755,10 @@
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C68" s="2">
         <v>15</v>
@@ -3720,10 +3776,11 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I68" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I68" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J68" s="2">
         <v>1760</v>
@@ -3731,10 +3788,10 @@
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C69" s="2">
         <v>10</v>
@@ -3752,10 +3809,11 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I69" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I69" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J69" s="2">
         <v>60</v>
@@ -3763,10 +3821,10 @@
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C70" s="2">
         <v>27</v>
@@ -3784,10 +3842,11 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I70" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I70" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J70" s="2">
         <v>937</v>
@@ -3795,10 +3854,10 @@
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C71" s="2">
         <v>23</v>
@@ -3816,10 +3875,11 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I71" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I71" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J71" s="2">
         <v>1923</v>
@@ -3827,10 +3887,10 @@
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C72" s="2">
         <v>46</v>
@@ -3848,10 +3908,11 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I72" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I72" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J72" s="2">
         <v>1200</v>
@@ -3859,10 +3920,10 @@
     </row>
     <row r="73" spans="1:10">
       <c r="A73" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C73" s="2">
         <v>32</v>
@@ -3880,10 +3941,11 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I73" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I73" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J73" s="2">
         <v>1936</v>
@@ -3891,10 +3953,10 @@
     </row>
     <row r="74" spans="1:10">
       <c r="A74" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C74" s="2">
         <v>87</v>
@@ -3912,10 +3974,11 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I74" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I74" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J74" s="2">
         <v>4573</v>
@@ -3923,10 +3986,10 @@
     </row>
     <row r="75" spans="1:10">
       <c r="A75" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C75" s="2">
         <v>49</v>
@@ -3944,10 +4007,11 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I75" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I75" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J75" s="2">
         <v>3437.5</v>
@@ -3955,10 +4019,10 @@
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C76" s="2">
         <v>22</v>
@@ -3976,10 +4040,11 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I76" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I76" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J76" s="2">
         <v>1500</v>
@@ -3987,10 +4052,10 @@
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C77" s="2">
         <v>1</v>
@@ -4008,10 +4073,11 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I77" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I77" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J77" s="2">
         <v>1440</v>
@@ -4019,10 +4085,10 @@
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C78" s="2">
         <v>110</v>
@@ -4040,10 +4106,11 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I78" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I78" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J78" s="2">
         <v>6808.46</v>
@@ -4051,10 +4118,10 @@
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C79" s="2">
         <v>76</v>
@@ -4072,10 +4139,11 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I79" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I79" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J79" s="2">
         <v>13806</v>
@@ -4083,10 +4151,10 @@
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C80" s="2">
         <v>35</v>
@@ -4104,10 +4172,11 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I80" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J80" s="2">
         <v>2509</v>
@@ -4115,10 +4184,10 @@
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C81" s="2">
         <v>36</v>
@@ -4136,10 +4205,11 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I81" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I81" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J81" s="2">
         <v>1930.85</v>
@@ -4147,10 +4217,10 @@
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C82" s="2">
         <v>56</v>
@@ -4168,10 +4238,11 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I82" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I82" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J82" s="2">
         <v>1200</v>
@@ -4179,10 +4250,10 @@
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C83" s="2">
         <v>204</v>
@@ -4200,10 +4271,11 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I83" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I83" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J83" s="2">
         <v>8066.75</v>
@@ -4211,10 +4283,10 @@
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C84" s="2">
         <v>26</v>
@@ -4232,10 +4304,11 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I84" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I84" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J84" s="2">
         <v>2800</v>
@@ -4243,10 +4316,10 @@
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C85" s="2">
         <v>28</v>
@@ -4264,10 +4337,11 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I85" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I85" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J85" s="2">
         <v>815</v>
@@ -4275,10 +4349,10 @@
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C86" s="2">
         <v>25</v>
@@ -4296,10 +4370,11 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I86" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I86" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J86" s="2">
         <v>1766</v>
@@ -4307,10 +4382,10 @@
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C87" s="2">
         <v>529</v>
@@ -4328,10 +4403,11 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I87" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I87" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J87" s="2">
         <v>12461</v>
@@ -4339,10 +4415,10 @@
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C88" s="2">
         <v>216</v>
@@ -4360,10 +4436,11 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I88" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I88" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J88" s="2">
         <v>1000</v>
@@ -4371,10 +4448,10 @@
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C89" s="2">
         <v>43</v>
@@ -4392,10 +4469,11 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I89" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I89" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J89" s="2">
         <v>5112</v>
@@ -4403,10 +4481,10 @@
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C90" s="2">
         <v>12</v>
@@ -4424,10 +4502,11 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I90" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I90" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J90" s="2">
         <v>2800</v>
@@ -4435,10 +4514,10 @@
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C91" s="2">
         <v>284</v>
@@ -4456,10 +4535,11 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I91" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I91" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J91" s="2">
         <v>1800</v>
@@ -4467,10 +4547,10 @@
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C92" s="2">
         <v>281</v>
@@ -4488,10 +4568,11 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I92" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I92" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J92" s="2">
         <v>2760</v>
@@ -4499,10 +4580,10 @@
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C93" s="2">
         <v>2</v>
@@ -4520,10 +4601,11 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I93" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I93" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J93" s="2">
         <v>1920</v>
@@ -4531,10 +4613,10 @@
     </row>
     <row r="94" spans="1:10">
       <c r="A94" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C94" s="2">
         <v>24</v>
@@ -4552,10 +4634,11 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I94" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I94" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J94" s="2">
         <v>5900</v>
@@ -4563,10 +4646,10 @@
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C95" s="2">
         <v>34</v>
@@ -4584,10 +4667,11 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I95" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I95" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J95" s="2">
         <v>1300</v>
@@ -4595,10 +4679,10 @@
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C96" s="2">
         <v>17</v>
@@ -4616,10 +4700,11 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I96" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I96" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J96" s="2">
         <v>200</v>
@@ -4627,10 +4712,10 @@
     </row>
     <row r="97" spans="1:10">
       <c r="A97" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C97" s="2">
         <v>11</v>
@@ -4648,10 +4733,11 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I97" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I97" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J97" s="2">
         <v>1825</v>
@@ -4659,10 +4745,10 @@
     </row>
     <row r="98" spans="1:10">
       <c r="A98" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C98" s="2">
         <v>115</v>
@@ -4680,10 +4766,11 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I98" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I98" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J98" s="2">
         <v>2849</v>
@@ -4691,10 +4778,10 @@
     </row>
     <row r="99" spans="1:10">
       <c r="A99" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C99" s="2">
         <v>64</v>
@@ -4712,10 +4799,11 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I99" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I99" s="2">
+        <f t="shared" ref="I99:I130" si="1">SUM(E99:G99)+1</f>
+        <v>1</v>
       </c>
       <c r="J99" s="2">
         <v>4927</v>
@@ -4723,10 +4811,10 @@
     </row>
     <row r="100" spans="1:10">
       <c r="A100" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C100" s="2">
         <v>50</v>
@@ -4744,10 +4832,11 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I100" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I100" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J100" s="2">
         <v>80</v>
@@ -4755,10 +4844,10 @@
     </row>
     <row r="101" spans="1:10">
       <c r="A101" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C101" s="2">
         <v>42</v>
@@ -4776,10 +4865,11 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I101" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I101" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J101" s="2">
         <v>68</v>
@@ -4787,10 +4877,10 @@
     </row>
     <row r="102" spans="1:10">
       <c r="A102" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C102" s="2">
         <v>11</v>
@@ -4808,10 +4898,11 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I102" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I102" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J102" s="2">
         <v>876</v>
@@ -4819,10 +4910,10 @@
     </row>
     <row r="103" spans="1:10">
       <c r="A103" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C103" s="2">
         <v>68</v>
@@ -4840,10 +4931,11 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I103" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I103" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J103" s="2">
         <v>361.96</v>
@@ -4851,10 +4943,10 @@
     </row>
     <row r="104" spans="1:10">
       <c r="A104" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C104" s="2">
         <v>76</v>
@@ -4872,10 +4964,11 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I104" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I104" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J104" s="2">
         <v>1440</v>
@@ -4883,10 +4976,10 @@
     </row>
     <row r="105" spans="1:10">
       <c r="A105" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C105" s="2">
         <v>293</v>
@@ -4904,10 +4997,11 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I105" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I105" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J105" s="2">
         <v>3060</v>
@@ -4915,10 +5009,10 @@
     </row>
     <row r="106" spans="1:10">
       <c r="A106" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C106" s="2">
         <v>38</v>
@@ -4936,10 +5030,11 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I106" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I106" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J106" s="2">
         <v>1020</v>
@@ -4947,10 +5042,10 @@
     </row>
     <row r="107" spans="1:10">
       <c r="A107" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C107" s="2">
         <v>111</v>
@@ -4968,10 +5063,11 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I107" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I107" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J107" s="2">
         <v>1080</v>
@@ -4979,10 +5075,10 @@
     </row>
     <row r="108" spans="1:10">
       <c r="A108" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C108" s="2">
         <v>137</v>
@@ -5000,10 +5096,11 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I108" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I108" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J108" s="2">
         <v>3698</v>
@@ -5011,10 +5108,10 @@
     </row>
     <row r="109" spans="1:10">
       <c r="A109" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C109" s="2">
         <v>47</v>
@@ -5032,10 +5129,11 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I109" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I109" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J109" s="2">
         <v>432</v>
@@ -5043,10 +5141,10 @@
     </row>
     <row r="110" spans="1:10">
       <c r="A110" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C110" s="2">
         <v>57</v>
@@ -5064,10 +5162,11 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I110" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I110" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J110" s="2">
         <v>1765</v>
@@ -5075,10 +5174,10 @@
     </row>
     <row r="111" spans="1:10">
       <c r="A111" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C111" s="2">
         <v>100</v>
@@ -5096,10 +5195,11 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I111" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I111" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J111" s="2">
         <v>20880</v>
@@ -5107,10 +5207,10 @@
     </row>
     <row r="112" spans="1:10">
       <c r="A112" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C112" s="2">
         <v>152</v>
@@ -5128,10 +5228,11 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I112" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I112" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J112" s="2">
         <v>5800</v>
@@ -5139,10 +5240,10 @@
     </row>
     <row r="113" spans="1:10">
       <c r="A113" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C113" s="2">
         <v>180</v>
@@ -5160,10 +5261,11 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I113" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I113" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J113" s="2">
         <v>6000</v>
@@ -5171,10 +5273,10 @@
     </row>
     <row r="114" spans="1:10">
       <c r="A114" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C114" s="2">
         <v>25</v>
@@ -5192,10 +5294,11 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I114" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I114" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J114" s="2">
         <v>2908</v>
@@ -5203,10 +5306,10 @@
     </row>
     <row r="115" spans="1:10">
       <c r="A115" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C115" s="2">
         <v>33</v>
@@ -5224,10 +5327,11 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I115" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I115" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J115" s="2">
         <v>2000</v>
@@ -5235,10 +5339,10 @@
     </row>
     <row r="116" spans="1:10">
       <c r="A116" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C116" s="2">
         <v>116</v>
@@ -5256,10 +5360,11 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I116" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I116" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J116" s="2">
         <v>1508.06</v>
@@ -5267,10 +5372,10 @@
     </row>
     <row r="117" spans="1:10">
       <c r="A117" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C117" s="2">
         <v>106</v>
@@ -5288,10 +5393,11 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I117" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I117" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J117" s="2">
         <v>7500</v>
@@ -5299,10 +5405,10 @@
     </row>
     <row r="118" spans="1:10">
       <c r="A118" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C118" s="2">
         <v>85</v>
@@ -5320,10 +5426,11 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I118" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I118" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J118" s="2">
         <v>4000</v>
@@ -5331,10 +5438,10 @@
     </row>
     <row r="119" spans="1:10">
       <c r="A119" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C119" s="2">
         <v>80</v>
@@ -5352,10 +5459,11 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I119" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I119" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J119" s="2">
         <v>4345</v>
@@ -5363,10 +5471,10 @@
     </row>
     <row r="120" spans="1:10">
       <c r="A120" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C120" s="2">
         <v>66</v>
@@ -5384,10 +5492,11 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I120" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I120" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J120" s="2">
         <v>4000</v>
@@ -5395,10 +5504,10 @@
     </row>
     <row r="121" spans="1:10">
       <c r="A121" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C121" s="2">
         <v>47</v>
@@ -5416,10 +5525,11 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I121" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I121" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J121" s="2">
         <v>1000</v>
@@ -5427,10 +5537,10 @@
     </row>
     <row r="122" spans="1:10">
       <c r="A122" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C122" s="2">
         <v>59</v>
@@ -5448,10 +5558,11 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I122" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I122" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J122" s="2">
         <v>960</v>
@@ -5459,10 +5570,10 @@
     </row>
     <row r="123" spans="1:10">
       <c r="A123" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C123" s="2">
         <v>133</v>
@@ -5480,10 +5591,11 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I123" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I123" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J123" s="2">
         <v>2830</v>
@@ -5491,10 +5603,10 @@
     </row>
     <row r="124" spans="1:10">
       <c r="A124" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C124" s="2">
         <v>131</v>
@@ -5512,10 +5624,11 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I124" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I124" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J124" s="2">
         <v>1673</v>
@@ -5523,10 +5636,10 @@
     </row>
     <row r="125" spans="1:10">
       <c r="A125" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C125" s="2">
         <v>100</v>
@@ -5544,10 +5657,11 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I125" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I125" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J125" s="2">
         <v>1500</v>
@@ -5555,10 +5669,10 @@
     </row>
     <row r="126" spans="1:10">
       <c r="A126" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C126" s="2">
         <v>26</v>
@@ -5576,10 +5690,11 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I126" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I126" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J126" s="2">
         <v>12036</v>
@@ -5587,10 +5702,10 @@
     </row>
     <row r="127" spans="1:10">
       <c r="A127" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C127" s="2">
         <v>71</v>
@@ -5608,10 +5723,11 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I127" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I127" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J127" s="2">
         <v>768.71</v>
@@ -5619,10 +5735,10 @@
     </row>
     <row r="128" spans="1:10">
       <c r="A128" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C128" s="2">
         <v>133</v>
@@ -5640,10 +5756,11 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I128" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I128" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J128" s="2">
         <v>1600</v>
@@ -5651,10 +5768,10 @@
     </row>
     <row r="129" spans="1:10">
       <c r="A129" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C129" s="2">
         <v>113</v>
@@ -5672,10 +5789,11 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I129" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I129" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J129" s="2">
         <v>3965</v>
@@ -5683,10 +5801,10 @@
     </row>
     <row r="130" spans="1:10">
       <c r="A130" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C130" s="2">
         <v>10</v>
@@ -5704,10 +5822,11 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I130" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I130" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J130" s="2">
         <v>600</v>
@@ -5715,10 +5834,10 @@
     </row>
     <row r="131" spans="1:10">
       <c r="A131" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C131" s="2">
         <v>108</v>
@@ -5736,10 +5855,11 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I131" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I131" s="2">
+        <f t="shared" ref="I131:I156" si="2">SUM(E131:G131)+1</f>
+        <v>1</v>
       </c>
       <c r="J131" s="2">
         <v>2470</v>
@@ -5747,10 +5867,10 @@
     </row>
     <row r="132" spans="1:10">
       <c r="A132" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C132" s="2">
         <v>8</v>
@@ -5768,10 +5888,11 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I132" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I132" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J132" s="2">
         <v>240</v>
@@ -5779,10 +5900,10 @@
     </row>
     <row r="133" spans="1:10">
       <c r="A133" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C133" s="2">
         <v>36</v>
@@ -5800,10 +5921,11 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I133" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I133" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J133" s="2">
         <v>3719</v>
@@ -5811,10 +5933,10 @@
     </row>
     <row r="134" spans="1:10">
       <c r="A134" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C134" s="2">
         <v>81</v>
@@ -5832,10 +5954,11 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I134" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I134" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J134" s="2">
         <v>2955.34</v>
@@ -5843,10 +5966,10 @@
     </row>
     <row r="135" spans="1:10">
       <c r="A135" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C135" s="2">
         <v>85</v>
@@ -5864,10 +5987,11 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I135" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I135" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J135" s="2">
         <v>660</v>
@@ -5875,10 +5999,10 @@
     </row>
     <row r="136" spans="1:10">
       <c r="A136" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C136" s="2">
         <v>24</v>
@@ -5896,10 +6020,11 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I136" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I136" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J136" s="2">
         <v>960</v>
@@ -5907,10 +6032,10 @@
     </row>
     <row r="137" spans="1:10">
       <c r="A137" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C137" s="2">
         <v>49</v>
@@ -5928,10 +6053,11 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I137" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I137" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J137" s="2">
         <v>720</v>
@@ -5939,10 +6065,10 @@
     </row>
     <row r="138" spans="1:10">
       <c r="A138" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C138" s="2">
         <v>6</v>
@@ -5960,10 +6086,11 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I138" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I138" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J138" s="2">
         <v>960</v>
@@ -5971,10 +6098,10 @@
     </row>
     <row r="139" spans="1:10">
       <c r="A139" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C139" s="2">
         <v>47</v>
@@ -5992,10 +6119,11 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I139" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I139" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J139" s="2">
         <v>1200</v>
@@ -6003,10 +6131,10 @@
     </row>
     <row r="140" spans="1:10">
       <c r="A140" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C140" s="2">
         <v>22</v>
@@ -6024,10 +6152,11 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I140" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I140" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J140" s="2">
         <v>840</v>
@@ -6035,10 +6164,10 @@
     </row>
     <row r="141" spans="1:10">
       <c r="A141" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C141" s="2">
         <v>15</v>
@@ -6056,10 +6185,11 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I141" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="I141" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J141" s="2">
         <v>1934</v>
@@ -6067,10 +6197,10 @@
     </row>
     <row r="142" spans="1:10">
       <c r="A142" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C142" s="2">
         <v>158</v>
@@ -6088,10 +6218,11 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="I142" s="2" t="s">
-        <v>13</v>
+        <v>161</v>
+      </c>
+      <c r="I142" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J142" s="2">
         <v>2927</v>
@@ -6099,10 +6230,10 @@
     </row>
     <row r="143" spans="1:10">
       <c r="A143" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C143" s="2">
         <v>4</v>
@@ -6120,10 +6251,11 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="I143" s="2" t="s">
-        <v>13</v>
+        <v>161</v>
+      </c>
+      <c r="I143" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J143" s="2">
         <v>1398</v>
@@ -6131,10 +6263,10 @@
     </row>
     <row r="144" spans="1:10">
       <c r="A144" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C144" s="2">
         <v>20</v>
@@ -6152,10 +6284,11 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="I144" s="2" t="s">
-        <v>13</v>
+        <v>161</v>
+      </c>
+      <c r="I144" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J144" s="2">
         <v>1693</v>
@@ -6163,10 +6296,10 @@
     </row>
     <row r="145" spans="1:10">
       <c r="A145" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C145" s="2">
         <v>25</v>
@@ -6184,10 +6317,11 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="I145" s="2" t="s">
-        <v>13</v>
+        <v>161</v>
+      </c>
+      <c r="I145" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J145" s="2">
         <v>1200</v>
@@ -6195,10 +6329,10 @@
     </row>
     <row r="146" spans="1:10">
       <c r="A146" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C146" s="2">
         <v>50</v>
@@ -6216,10 +6350,11 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="I146" s="2" t="s">
-        <v>13</v>
+        <v>161</v>
+      </c>
+      <c r="I146" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J146" s="2">
         <v>1075.54</v>
@@ -6227,10 +6362,10 @@
     </row>
     <row r="147" spans="1:10">
       <c r="A147" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C147" s="2">
         <v>16</v>
@@ -6248,10 +6383,11 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="I147" s="2" t="s">
-        <v>13</v>
+        <v>161</v>
+      </c>
+      <c r="I147" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J147" s="2">
         <v>480</v>
@@ -6259,10 +6395,10 @@
     </row>
     <row r="148" spans="1:10">
       <c r="A148" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C148" s="2">
         <v>4</v>
@@ -6280,10 +6416,11 @@
         <v>0</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="I148" s="2" t="s">
-        <v>13</v>
+        <v>161</v>
+      </c>
+      <c r="I148" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J148" s="2">
         <v>1400</v>
@@ -6291,10 +6428,10 @@
     </row>
     <row r="149" spans="1:10">
       <c r="A149" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C149" s="2">
         <v>13</v>
@@ -6312,10 +6449,11 @@
         <v>0</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="I149" s="2" t="s">
-        <v>13</v>
+        <v>161</v>
+      </c>
+      <c r="I149" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J149" s="2">
         <v>1193.55</v>
@@ -6323,10 +6461,10 @@
     </row>
     <row r="150" spans="1:10">
       <c r="A150" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C150" s="2">
         <v>9</v>
@@ -6344,10 +6482,11 @@
         <v>0</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="I150" s="2" t="s">
-        <v>13</v>
+        <v>161</v>
+      </c>
+      <c r="I150" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J150" s="2">
         <v>341.28</v>
@@ -6355,10 +6494,10 @@
     </row>
     <row r="151" spans="1:10">
       <c r="A151" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C151" s="2">
         <v>1</v>
@@ -6376,10 +6515,11 @@
         <v>0</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="I151" s="2" t="s">
-        <v>13</v>
+        <v>161</v>
+      </c>
+      <c r="I151" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J151" s="2">
         <v>360</v>
@@ -6387,10 +6527,10 @@
     </row>
     <row r="152" spans="1:10">
       <c r="A152" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C152" s="2">
         <v>39</v>
@@ -6408,10 +6548,11 @@
         <v>0</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="I152" s="2" t="s">
-        <v>13</v>
+        <v>161</v>
+      </c>
+      <c r="I152" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J152" s="2">
         <v>1804</v>
@@ -6419,10 +6560,10 @@
     </row>
     <row r="153" spans="1:10">
       <c r="A153" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C153" s="2">
         <v>5</v>
@@ -6440,10 +6581,11 @@
         <v>0</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="I153" s="2" t="s">
-        <v>13</v>
+        <v>161</v>
+      </c>
+      <c r="I153" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J153" s="2">
         <v>960</v>
@@ -6451,10 +6593,10 @@
     </row>
     <row r="154" spans="1:10">
       <c r="A154" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C154" s="2">
         <v>37</v>
@@ -6472,10 +6614,11 @@
         <v>0</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="I154" s="2" t="s">
-        <v>13</v>
+        <v>161</v>
+      </c>
+      <c r="I154" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J154" s="2">
         <v>2240</v>
@@ -6483,10 +6626,10 @@
     </row>
     <row r="155" spans="1:10">
       <c r="A155" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C155" s="2">
         <v>15</v>
@@ -6504,10 +6647,11 @@
         <v>0</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="I155" s="2" t="s">
-        <v>13</v>
+        <v>161</v>
+      </c>
+      <c r="I155" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J155" s="2">
         <v>482</v>
@@ -6515,10 +6659,10 @@
     </row>
     <row r="156" spans="1:10">
       <c r="A156" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C156" s="2">
         <v>66</v>
@@ -6536,10 +6680,11 @@
         <v>0</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="I156" s="2" t="s">
-        <v>13</v>
+        <v>161</v>
+      </c>
+      <c r="I156" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="J156" s="2">
         <v>522</v>
@@ -6547,7 +6692,7 @@
     </row>
   </sheetData>
   <sortState ref="A2:J156">
-    <sortCondition ref="H28"/>
+    <sortCondition ref="I2" descending="1"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
